--- a/Result/profitability/4109.xlsx
+++ b/Result/profitability/4109.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05124999999999995</v>
+        <v>-0.007500000000000059</v>
       </c>
       <c r="N2" t="n">
-        <v>30.92375</v>
+        <v>30.2525</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04874999999999994</v>
+        <v>0.01874999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>30.6175</v>
+        <v>29.9075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08874999999999994</v>
+        <v>0.01874999999999994</v>
       </c>
       <c r="N4" t="n">
-        <v>30.2425</v>
+        <v>29.12125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1020,10 +1020,10 @@
         <v>0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1025</v>
+        <v>0.04874999999999995</v>
       </c>
       <c r="N5" t="n">
-        <v>29.57</v>
+        <v>28.47</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1035,13 +1035,13 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1187499999999999</v>
+        <v>0.05249999999999994</v>
       </c>
       <c r="N6" t="n">
-        <v>29.0975</v>
+        <v>28.99</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.105</v>
+        <v>0.02124999999999995</v>
       </c>
       <c r="N7" t="n">
-        <v>29.9475</v>
+        <v>30.24</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1124999999999999</v>
+        <v>0.03874999999999994</v>
       </c>
       <c r="N8" t="n">
-        <v>30.725</v>
+        <v>30.56875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
         <v>0.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08249999999999993</v>
+        <v>0.08249999999999995</v>
       </c>
       <c r="N13" t="n">
         <v>34.0725</v>
@@ -9842,6 +9842,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4109</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>133</v>
+      </c>
+      <c r="D75" t="n">
+        <v>97</v>
+      </c>
+      <c r="E75" t="n">
+        <v>36</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-48</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-48</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-53</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.003750000000000059</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.61375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.933333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04418522446094031</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-8.800000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2455357142857144</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
